--- a/cdlqi_results.xlsx
+++ b/cdlqi_results.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,16 +501,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>341440758</v>
+        <v>410830374</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>squeaz</t>
+          <t>id410830374</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-03-09 18:57:12</t>
+          <t>2026-03-29 14:06:41</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -526,154 +526,154 @@
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Значительное — влияет на учёбу и общение.</t>
+          <t>Значительное влияние</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>885305710</v>
+        <v>410830374</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>darovskikh_ma</t>
+          <t>id410830374</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-03-09 19:08:21</t>
+          <t>2026-03-29 14:07:12</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Значительное — влияет на учёбу и общение.</t>
+          <t>Умеренное влияние</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>341440758</v>
+        <v>410830374</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>squeaz</t>
+          <t>id410830374</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-03-09 19:34:15</t>
+          <t>2026-03-29 14:17:19</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4</v>
-      </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Значительное — влияет на учёбу и общение.</t>
+          <t>Значительное — влияет на учёбу и общение</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>341440758</v>
+        <v>410830374</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>squeaz</t>
+          <t>id410830374</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-03-09 19:39:44</t>
+          <t>2026-03-29 14:52:52</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -685,400 +685,29 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
         <v>2</v>
       </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Значительное — влияет на учёбу и общение.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1299948387</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>anastasiia_mez</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-03-09 19:44:56</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>28</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Экстремальное — депрессия, шрамы, срочно к дерматологу!</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>341440758</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>squeaz</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-03-09 19:58:20</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>12</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Значительное — влияет на учёбу и общение.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>341440758</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>squeaz</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-03-09 19:59:17</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" t="n">
-        <v>17</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Значительное — влияет на учёбу и общение.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>341440758</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>squeaz</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-03-09 20:15:48</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>18</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Значительное — влияет на учёбу и общение.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>341440758</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>squeaz</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-03-09 20:16:49</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Лёгкое — комедоны, лёгкое воспаление.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>341440758</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>squeaz</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-03-09 20:28:48</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>11</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Значительное — влияет на учёбу и общение.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>341440758</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>squeaz</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026-03-09 20:29:23</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Минимальное — акне не мешает жизни.</t>
+          <t>Значительное — влияет на учёбу и общение</t>
         </is>
       </c>
     </row>
